--- a/analysis/econometrics_outputs/contdid/Graficos/unemployment/dose/contdid_rf_dose_acrt.xlsx
+++ b/analysis/econometrics_outputs/contdid/Graficos/unemployment/dose/contdid_rf_dose_acrt.xlsx
@@ -488,10 +488,10 @@
         <v>5.68342046462609</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>3.96557539463369</v>
+        <v>4.14860012532495</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>10.4514113986012</v>
+        <v>2.68805809220553</v>
       </c>
       <c r="H6" s="1"/>
       <c r="I6" s="1"/>
@@ -510,10 +510,10 @@
         <v>5.44258650228273</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>3.65387689755813</v>
+        <v>3.89335109215028</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>10.4514113986012</v>
+        <v>2.68805809220553</v>
       </c>
       <c r="H7" s="1"/>
       <c r="I7" s="1"/>
@@ -532,10 +532,10 @@
         <v>5.08897020459553</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>3.19977219663933</v>
+        <v>3.51898784805325</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>10.4514113986012</v>
+        <v>2.68805809220553</v>
       </c>
       <c r="H8" s="1"/>
       <c r="I8" s="1"/>
@@ -554,10 +554,10 @@
         <v>4.87847620799186</v>
       </c>
       <c r="F9" s="1" t="n">
-        <v>2.93165497810008</v>
+        <v>3.26374147309606</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>10.4514113986012</v>
+        <v>2.68805809220553</v>
       </c>
       <c r="H9" s="1"/>
       <c r="I9" s="1"/>
@@ -576,10 +576,10 @@
         <v>4.46070822612599</v>
       </c>
       <c r="F10" s="1" t="n">
-        <v>2.40495185839887</v>
+        <v>2.79678042429004</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>10.4514113986012</v>
+        <v>2.68805809220553</v>
       </c>
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
@@ -598,10 +598,10 @@
         <v>4.26815329014965</v>
       </c>
       <c r="F11" s="1" t="n">
-        <v>2.16487732293157</v>
+        <v>2.58329911554966</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>10.4514113986012</v>
+        <v>2.68805809220553</v>
       </c>
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
@@ -620,10 +620,10 @@
         <v>4.17671501009938</v>
       </c>
       <c r="F12" s="1" t="n">
-        <v>2.05152431370255</v>
+        <v>2.48188604802444</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>10.4514113986012</v>
+        <v>2.68805809220553</v>
       </c>
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
@@ -642,10 +642,10 @@
         <v>4.07333302791999</v>
       </c>
       <c r="F13" s="1" t="n">
-        <v>1.92389744526037</v>
+        <v>2.3684314301506</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>10.4514113986012</v>
+        <v>2.68805809220553</v>
       </c>
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
@@ -664,10 +664,10 @@
         <v>3.99082245885884</v>
       </c>
       <c r="F14" s="1" t="n">
-        <v>1.82245841330527</v>
+        <v>2.26017841727766</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>10.4514113986012</v>
+        <v>2.68805809220553</v>
       </c>
       <c r="H14" s="1"/>
       <c r="I14" s="1"/>
@@ -686,10 +686,10 @@
         <v>3.78776831051149</v>
       </c>
       <c r="F15" s="1" t="n">
-        <v>1.57451093927953</v>
+        <v>1.9631069417535</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>10.4514113986012</v>
+        <v>2.68805809220553</v>
       </c>
       <c r="H15" s="1"/>
       <c r="I15" s="1"/>
@@ -708,10 +708,10 @@
         <v>3.64822579494429</v>
       </c>
       <c r="F16" s="1" t="n">
-        <v>1.40560308526985</v>
+        <v>1.83904322064409</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>10.4514113986012</v>
+        <v>2.68805809220553</v>
       </c>
       <c r="H16" s="1"/>
       <c r="I16" s="1"/>
@@ -730,10 +730,10 @@
         <v>3.43998931447721</v>
       </c>
       <c r="F17" s="1" t="n">
-        <v>1.15600576525964</v>
+        <v>1.54157631483904</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>10.4514113986012</v>
+        <v>2.68805809220553</v>
       </c>
       <c r="H17" s="1"/>
       <c r="I17" s="1"/>
@@ -752,10 +752,10 @@
         <v>3.31126217071424</v>
       </c>
       <c r="F18" s="1" t="n">
-        <v>1.00330865993262</v>
+        <v>1.45336966043774</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>10.4514113986012</v>
+        <v>2.68805809220553</v>
       </c>
       <c r="H18" s="1"/>
       <c r="I18" s="1"/>
@@ -774,10 +774,10 @@
         <v>3.24003774480832</v>
       </c>
       <c r="F19" s="1" t="n">
-        <v>0.919385979573474</v>
+        <v>1.38001472066612</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>10.4514113986012</v>
+        <v>2.68805809220553</v>
       </c>
       <c r="H19" s="1"/>
       <c r="I19" s="1"/>
@@ -796,10 +796,10 @@
         <v>3.11865352362018</v>
       </c>
       <c r="F20" s="1" t="n">
-        <v>0.777344637636686</v>
+        <v>1.24175113229412</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>10.4514113986012</v>
+        <v>2.68805809220553</v>
       </c>
       <c r="H20" s="1"/>
       <c r="I20" s="1"/>
@@ -818,10 +818,10 @@
         <v>2.82008079272961</v>
       </c>
       <c r="F21" s="1" t="n">
-        <v>0.504895603321579</v>
+        <v>1.02144242754944</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>10.4514113986012</v>
+        <v>2.68805809220553</v>
       </c>
       <c r="H21" s="1"/>
       <c r="I21" s="1"/>
@@ -840,10 +840,10 @@
         <v>2.72379247594386</v>
       </c>
       <c r="F22" s="1" t="n">
-        <v>0.418974955248623</v>
+        <v>0.937678584429112</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>10.4514113986012</v>
+        <v>2.68805809220553</v>
       </c>
       <c r="H22" s="1"/>
       <c r="I22" s="1"/>
@@ -862,10 +862,10 @@
         <v>2.58661618570804</v>
       </c>
       <c r="F23" s="1" t="n">
-        <v>0.298075085856971</v>
+        <v>0.826450789145923</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>10.4514113986012</v>
+        <v>2.68805809220553</v>
       </c>
       <c r="H23" s="1"/>
       <c r="I23" s="1"/>
@@ -884,10 +884,10 @@
         <v>2.45565593408061</v>
       </c>
       <c r="F24" s="1" t="n">
-        <v>0.184460442264459</v>
+        <v>0.734047585606726</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>10.4514113986012</v>
+        <v>2.68805809220553</v>
       </c>
       <c r="H24" s="1"/>
       <c r="I24" s="1"/>
@@ -906,10 +906,10 @@
         <v>2.35303368014537</v>
       </c>
       <c r="F25" s="1" t="n">
-        <v>0.180105862289308</v>
+        <v>0.710534819180375</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>10.4514113986012</v>
+        <v>2.68805809220553</v>
       </c>
       <c r="H25" s="1"/>
       <c r="I25" s="1"/>
@@ -928,10 +928,10 @@
         <v>2.22801905749965</v>
       </c>
       <c r="F26" s="1" t="n">
-        <v>0.21648802511328</v>
+        <v>0.649116068089536</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>10.4514113986012</v>
+        <v>2.68805809220553</v>
       </c>
       <c r="H26" s="1"/>
       <c r="I26" s="1"/>
@@ -950,10 +950,10 @@
         <v>2.12116941596883</v>
       </c>
       <c r="F27" s="1" t="n">
-        <v>0.319891722678583</v>
+        <v>0.610806918595158</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>10.4514113986012</v>
+        <v>2.68805809220553</v>
       </c>
       <c r="H27" s="1"/>
       <c r="I27" s="1"/>
@@ -972,10 +972,10 @@
         <v>1.98158322064554</v>
       </c>
       <c r="F28" s="1" t="n">
-        <v>0.282760891548681</v>
+        <v>0.622168566797001</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>10.4514113986012</v>
+        <v>2.68805809220553</v>
       </c>
       <c r="H28" s="1"/>
       <c r="I28" s="1"/>
@@ -994,10 +994,10 @@
         <v>1.80939484855205</v>
       </c>
       <c r="F29" s="1" t="n">
-        <v>0.342332753612117</v>
+        <v>0.663484123750217</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>10.4514113986012</v>
+        <v>2.68805809220553</v>
       </c>
       <c r="H29" s="1"/>
       <c r="I29" s="1"/>
@@ -1016,10 +1016,10 @@
         <v>1.76810686638604</v>
       </c>
       <c r="F30" s="1" t="n">
-        <v>0.373484529396863</v>
+        <v>0.644094796963696</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>10.4514113986012</v>
+        <v>2.68805809220553</v>
       </c>
       <c r="H30" s="1"/>
       <c r="I30" s="1"/>
@@ -1038,10 +1038,10 @@
         <v>1.5786247057473</v>
       </c>
       <c r="F31" s="1" t="n">
-        <v>0.511070794442288</v>
+        <v>0.667206888908417</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>10.4514113986012</v>
+        <v>2.68805809220553</v>
       </c>
       <c r="H31" s="1"/>
       <c r="I31" s="1"/>
@@ -1060,10 +1060,10 @@
         <v>1.53315063999127</v>
       </c>
       <c r="F32" s="1" t="n">
-        <v>0.54259274599872</v>
+        <v>0.644662663491505</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>10.4514113986012</v>
+        <v>2.68805809220553</v>
       </c>
       <c r="H32" s="1"/>
       <c r="I32" s="1"/>
@@ -1082,10 +1082,10 @@
         <v>1.48861495204399</v>
       </c>
       <c r="F33" s="1" t="n">
-        <v>0.572817711242499</v>
+        <v>0.628743411952364</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>10.4514113986012</v>
+        <v>2.68805809220553</v>
       </c>
       <c r="H33" s="1"/>
       <c r="I33" s="1"/>
@@ -1104,10 +1104,10 @@
         <v>1.37037952353218</v>
       </c>
       <c r="F34" s="1" t="n">
-        <v>0.649562172809497</v>
+        <v>0.615593057456145</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>10.4514113986012</v>
+        <v>2.68805809220553</v>
       </c>
       <c r="H34" s="1"/>
       <c r="I34" s="1"/>
@@ -1126,10 +1126,10 @@
         <v>1.30431292858117</v>
       </c>
       <c r="F35" s="1" t="n">
-        <v>0.6898945711605</v>
+        <v>0.693175620504453</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>10.4514113986012</v>
+        <v>2.68805809220553</v>
       </c>
       <c r="H35" s="1"/>
       <c r="I35" s="1"/>
@@ -1148,10 +1148,10 @@
         <v>1.25394220207551</v>
       </c>
       <c r="F36" s="1" t="n">
-        <v>0.719208104376058</v>
+        <v>0.727694236977372</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>10.4514113986012</v>
+        <v>2.68805809220553</v>
       </c>
       <c r="H36" s="1"/>
       <c r="I36" s="1"/>
@@ -1170,10 +1170,10 @@
         <v>1.12582964636567</v>
       </c>
       <c r="F37" s="1" t="n">
-        <v>0.774365691386973</v>
+        <v>0.790559030438062</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>10.4514113986012</v>
+        <v>2.68805809220553</v>
       </c>
       <c r="H37" s="1"/>
       <c r="I37" s="1"/>
@@ -1192,10 +1192,10 @@
         <v>1.06907412458736</v>
       </c>
       <c r="F38" s="1" t="n">
-        <v>0.776053623621538</v>
+        <v>0.810316287488817</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>10.4514113986012</v>
+        <v>2.68805809220553</v>
       </c>
       <c r="H38" s="1"/>
       <c r="I38" s="1"/>
@@ -1214,10 +1214,10 @@
         <v>0.982528325908291</v>
       </c>
       <c r="F39" s="1" t="n">
-        <v>0.83388438785269</v>
+        <v>0.882035808337171</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>10.4514113986012</v>
+        <v>2.68805809220553</v>
       </c>
       <c r="H39" s="1"/>
       <c r="I39" s="1"/>
@@ -1236,10 +1236,10 @@
         <v>0.923142633979076</v>
       </c>
       <c r="F40" s="1" t="n">
-        <v>0.865221395810395</v>
+        <v>0.920875365763022</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>10.4514113986012</v>
+        <v>2.68805809220553</v>
       </c>
       <c r="H40" s="1"/>
       <c r="I40" s="1"/>
@@ -1258,10 +1258,10 @@
         <v>0.888619233105255</v>
       </c>
       <c r="F41" s="1" t="n">
-        <v>0.873134174102133</v>
+        <v>0.962701718783763</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>10.4514113986012</v>
+        <v>2.68805809220553</v>
       </c>
       <c r="H41" s="1"/>
       <c r="I41" s="1"/>
@@ -1280,10 +1280,10 @@
         <v>0.837868074322023</v>
       </c>
       <c r="F42" s="1" t="n">
-        <v>0.880395748765589</v>
+        <v>0.995237585956726</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>10.4514113986012</v>
+        <v>2.68805809220553</v>
       </c>
       <c r="H42" s="1"/>
       <c r="I42" s="1"/>
@@ -1302,10 +1302,10 @@
         <v>0.67871355734242</v>
       </c>
       <c r="F43" s="1" t="n">
-        <v>0.838012362026835</v>
+        <v>0.887989285007936</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>10.4514113986012</v>
+        <v>2.68805809220553</v>
       </c>
       <c r="H43" s="1"/>
       <c r="I43" s="1"/>
@@ -1324,10 +1324,10 @@
         <v>0.657929697220101</v>
       </c>
       <c r="F44" s="1" t="n">
-        <v>0.815168980505451</v>
+        <v>0.881951114151987</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>10.4514113986012</v>
+        <v>2.68805809220553</v>
       </c>
       <c r="H44" s="1"/>
       <c r="I44" s="1"/>
@@ -1346,10 +1346,10 @@
         <v>0.647031257983774</v>
       </c>
       <c r="F45" s="1" t="n">
-        <v>0.798783193088445</v>
+        <v>0.875841083094685</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>10.4514113986012</v>
+        <v>2.68805809220553</v>
       </c>
       <c r="H45" s="1"/>
       <c r="I45" s="1"/>
@@ -1368,10 +1368,10 @@
         <v>0.611153446221326</v>
       </c>
       <c r="F46" s="1" t="n">
-        <v>0.6617095725769</v>
+        <v>0.843398372487391</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>10.4514113986012</v>
+        <v>2.68805809220553</v>
       </c>
       <c r="H46" s="1"/>
       <c r="I46" s="1"/>
@@ -1390,10 +1390,10 @@
         <v>0.607181734640501</v>
       </c>
       <c r="F47" s="1" t="n">
-        <v>0.59525233760408</v>
+        <v>0.840050896781324</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>10.4514113986012</v>
+        <v>2.68805809220553</v>
       </c>
       <c r="H47" s="1"/>
       <c r="I47" s="1"/>
@@ -1412,10 +1412,10 @@
         <v>0.604311673522697</v>
       </c>
       <c r="F48" s="1" t="n">
-        <v>0.546181876744627</v>
+        <v>0.844884250679634</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>10.4514113986012</v>
+        <v>2.68805809220553</v>
       </c>
       <c r="H48" s="1"/>
       <c r="I48" s="1"/>
@@ -1434,10 +1434,10 @@
         <v>0.596783384346807</v>
       </c>
       <c r="F49" s="1" t="n">
-        <v>0.412379224822193</v>
+        <v>0.798622937045787</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>10.4514113986012</v>
+        <v>2.68805809220553</v>
       </c>
       <c r="H49" s="1"/>
       <c r="I49" s="1"/>
@@ -1456,10 +1456,10 @@
         <v>0.595135056848288</v>
       </c>
       <c r="F50" s="1" t="n">
-        <v>0.381901715765011</v>
+        <v>0.766223825913762</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>10.4514113986012</v>
+        <v>2.68805809220553</v>
       </c>
       <c r="H50" s="1"/>
       <c r="I50" s="1"/>
@@ -1478,10 +1478,10 @@
         <v>0.588546654149002</v>
       </c>
       <c r="F51" s="1" t="n">
-        <v>0.259713898749954</v>
+        <v>0.682705496866774</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>10.4514113986012</v>
+        <v>2.68805809220553</v>
       </c>
       <c r="H51" s="1"/>
       <c r="I51" s="1"/>
@@ -1500,10 +1500,10 @@
         <v>0.587555601449143</v>
       </c>
       <c r="F52" s="1" t="n">
-        <v>0.253396455049443</v>
+        <v>0.679002527584833</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>10.4514113986012</v>
+        <v>2.68805809220553</v>
       </c>
       <c r="H52" s="1"/>
       <c r="I52" s="1"/>
@@ -1522,10 +1522,10 @@
         <v>0.583817068425536</v>
       </c>
       <c r="F53" s="1" t="n">
-        <v>0.228691037907526</v>
+        <v>0.693810365656291</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>10.4514113986012</v>
+        <v>2.68805809220553</v>
       </c>
       <c r="H53" s="1"/>
       <c r="I53" s="1"/>
@@ -1544,10 +1544,10 @@
         <v>0.583150675247523</v>
       </c>
       <c r="F54" s="1" t="n">
-        <v>0.224118431669545</v>
+        <v>0.681951598506819</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>10.4514113986012</v>
+        <v>2.68805809220553</v>
       </c>
       <c r="H54" s="1"/>
       <c r="I54" s="1"/>
@@ -1566,10 +1566,10 @@
         <v>0.581121375152937</v>
       </c>
       <c r="F55" s="1" t="n">
-        <v>0.209809646094593</v>
+        <v>0.654974958382365</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>10.4514113986012</v>
+        <v>2.68805809220553</v>
       </c>
       <c r="H55" s="1"/>
       <c r="I55" s="1"/>
@@ -1588,10 +1588,10 @@
         <v>0.578588043707798</v>
       </c>
       <c r="F56" s="1" t="n">
-        <v>0.190960367310622</v>
+        <v>0.599930908064749</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>10.4514113986012</v>
+        <v>2.68805809220553</v>
       </c>
       <c r="H56" s="1"/>
       <c r="I56" s="1"/>
@@ -1610,10 +1610,10 @@
         <v>0.574809609350619</v>
       </c>
       <c r="F57" s="1" t="n">
-        <v>0.215974994504627</v>
+        <v>0.593223200625008</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>10.4514113986012</v>
+        <v>2.68805809220553</v>
       </c>
       <c r="H57" s="1"/>
       <c r="I57" s="1"/>
@@ -1632,10 +1632,10 @@
         <v>0.573780051580909</v>
       </c>
       <c r="F58" s="1" t="n">
-        <v>0.207610305495879</v>
+        <v>0.594708712007538</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>10.4514113986012</v>
+        <v>2.68805809220553</v>
       </c>
       <c r="H58" s="1"/>
       <c r="I58" s="1"/>
@@ -1654,10 +1654,10 @@
         <v>0.570398713943644</v>
       </c>
       <c r="F59" s="1" t="n">
-        <v>0.126834759971964</v>
+        <v>0.548687611768395</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>10.4514113986012</v>
+        <v>2.68805809220553</v>
       </c>
       <c r="H59" s="1"/>
       <c r="I59" s="1"/>
@@ -1676,10 +1676,10 @@
         <v>0.569619172475562</v>
       </c>
       <c r="F60" s="1" t="n">
-        <v>0.127782155350698</v>
+        <v>0.507754491743862</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>10.4514113986012</v>
+        <v>2.68805809220553</v>
       </c>
       <c r="H60" s="1"/>
       <c r="I60" s="1"/>
@@ -1698,10 +1698,10 @@
         <v>0.568770447817768</v>
       </c>
       <c r="F61" s="1" t="n">
-        <v>0.14593496151194</v>
+        <v>0.508316108665415</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>10.4514113986012</v>
+        <v>2.68805809220553</v>
       </c>
       <c r="H61" s="1"/>
       <c r="I61" s="1"/>
@@ -1720,10 +1720,10 @@
         <v>0.568046984925221</v>
       </c>
       <c r="F62" s="1" t="n">
-        <v>0.228701226959665</v>
+        <v>0.502735803117639</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>10.4514113986012</v>
+        <v>2.68805809220553</v>
       </c>
       <c r="H62" s="1"/>
       <c r="I62" s="1"/>
@@ -1742,10 +1742,10 @@
         <v>0.567921660163214</v>
       </c>
       <c r="F63" s="1" t="n">
-        <v>0.31266508598406</v>
+        <v>0.49670920396514</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>10.4514113986012</v>
+        <v>2.68805809220553</v>
       </c>
       <c r="H63" s="1"/>
       <c r="I63" s="1"/>
@@ -1764,10 +1764,10 @@
         <v>0.568358321785793</v>
       </c>
       <c r="F64" s="1" t="n">
-        <v>0.378265276528506</v>
+        <v>0.471867608361999</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>10.4514113986012</v>
+        <v>2.68805809220553</v>
       </c>
       <c r="H64" s="1"/>
       <c r="I64" s="1"/>
@@ -1786,10 +1786,10 @@
         <v>0.568949283594771</v>
       </c>
       <c r="F65" s="1" t="n">
-        <v>0.420662163816113</v>
+        <v>0.46497108697766</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>10.4514113986012</v>
+        <v>2.68805809220553</v>
       </c>
       <c r="H65" s="1"/>
       <c r="I65" s="1"/>
@@ -1808,10 +1808,10 @@
         <v>0.569803331393001</v>
       </c>
       <c r="F66" s="1" t="n">
-        <v>0.46181071759356</v>
+        <v>0.46730793554823</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>10.4514113986012</v>
+        <v>2.68805809220553</v>
       </c>
       <c r="H66" s="1"/>
       <c r="I66" s="1"/>
@@ -1830,10 +1830,10 @@
         <v>0.570195574820108</v>
       </c>
       <c r="F67" s="1" t="n">
-        <v>0.476878792492075</v>
+        <v>0.461747462503214</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>10.4514113986012</v>
+        <v>2.68805809220553</v>
       </c>
       <c r="H67" s="1"/>
       <c r="I67" s="1"/>
@@ -1852,10 +1852,10 @@
         <v>0.570681515489457</v>
       </c>
       <c r="F68" s="1" t="n">
-        <v>0.493434095056885</v>
+        <v>0.465909839844499</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>10.4514113986012</v>
+        <v>2.68805809220553</v>
       </c>
       <c r="H68" s="1"/>
       <c r="I68" s="1"/>
@@ -1874,10 +1874,10 @@
         <v>0.570982430095801</v>
       </c>
       <c r="F69" s="1" t="n">
-        <v>0.50276133469049</v>
+        <v>0.470407685352992</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>10.4514113986012</v>
+        <v>2.68805809220553</v>
       </c>
       <c r="H69" s="1"/>
       <c r="I69" s="1"/>
@@ -1896,10 +1896,10 @@
         <v>0.578093232475562</v>
       </c>
       <c r="F70" s="1" t="n">
-        <v>0.616883376118509</v>
+        <v>0.552602756343685</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>10.4514113986012</v>
+        <v>2.68805809220553</v>
       </c>
       <c r="H70" s="1"/>
       <c r="I70" s="1"/>
@@ -1918,10 +1918,10 @@
         <v>0.580800793984356</v>
       </c>
       <c r="F71" s="1" t="n">
-        <v>0.640982012659555</v>
+        <v>0.538763725361083</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>10.4514113986012</v>
+        <v>2.68805809220553</v>
       </c>
       <c r="H71" s="1"/>
       <c r="I71" s="1"/>
@@ -1940,10 +1940,10 @@
         <v>0.583916541186294</v>
       </c>
       <c r="F72" s="1" t="n">
-        <v>0.663421215187935</v>
+        <v>0.522754533143231</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>10.4514113986012</v>
+        <v>2.68805809220553</v>
       </c>
       <c r="H72" s="1"/>
       <c r="I72" s="1"/>
@@ -1962,10 +1962,10 @@
         <v>0.588789306387503</v>
       </c>
       <c r="F73" s="1" t="n">
-        <v>0.68163657129649</v>
+        <v>0.553476475561703</v>
       </c>
       <c r="G73" s="1" t="n">
-        <v>10.4514113986012</v>
+        <v>2.68805809220553</v>
       </c>
       <c r="H73" s="1"/>
       <c r="I73" s="1"/>
@@ -1984,10 +1984,10 @@
         <v>0.591573227209739</v>
       </c>
       <c r="F74" s="1" t="n">
-        <v>0.687854670952686</v>
+        <v>0.576957210330377</v>
       </c>
       <c r="G74" s="1" t="n">
-        <v>10.4514113986012</v>
+        <v>2.68805809220553</v>
       </c>
       <c r="H74" s="1"/>
       <c r="I74" s="1"/>
@@ -2006,10 +2006,10 @@
         <v>0.595491632104274</v>
       </c>
       <c r="F75" s="1" t="n">
-        <v>0.694527002602684</v>
+        <v>0.548962196671901</v>
       </c>
       <c r="G75" s="1" t="n">
-        <v>10.4514113986012</v>
+        <v>2.68805809220553</v>
       </c>
       <c r="H75" s="1"/>
       <c r="I75" s="1"/>
@@ -2028,10 +2028,10 @@
         <v>0.59843626190208</v>
       </c>
       <c r="F76" s="1" t="n">
-        <v>0.698216643445811</v>
+        <v>0.557036526351672</v>
       </c>
       <c r="G76" s="1" t="n">
-        <v>10.4514113986012</v>
+        <v>2.68805809220553</v>
       </c>
       <c r="H76" s="1"/>
       <c r="I76" s="1"/>
@@ -2050,10 +2050,10 @@
         <v>0.604458286713793</v>
       </c>
       <c r="F77" s="1" t="n">
-        <v>0.702916166292531</v>
+        <v>0.580002256430276</v>
       </c>
       <c r="G77" s="1" t="n">
-        <v>10.4514113986012</v>
+        <v>2.68805809220553</v>
       </c>
       <c r="H77" s="1"/>
       <c r="I77" s="1"/>
@@ -2072,10 +2072,10 @@
         <v>0.610665653591578</v>
       </c>
       <c r="F78" s="1" t="n">
-        <v>0.704551002120907</v>
+        <v>0.557703531748814</v>
       </c>
       <c r="G78" s="1" t="n">
-        <v>10.4514113986012</v>
+        <v>2.68805809220553</v>
       </c>
       <c r="H78" s="1"/>
       <c r="I78" s="1"/>
@@ -2094,10 +2094,10 @@
         <v>0.633550240954697</v>
       </c>
       <c r="F79" s="1" t="n">
-        <v>0.691605958597052</v>
+        <v>0.597823300566268</v>
       </c>
       <c r="G79" s="1" t="n">
-        <v>10.4514113986012</v>
+        <v>2.68805809220553</v>
       </c>
       <c r="H79" s="1"/>
       <c r="I79" s="1"/>
@@ -2116,10 +2116,10 @@
         <v>0.6424177701678</v>
       </c>
       <c r="F80" s="1" t="n">
-        <v>0.680961819645707</v>
+        <v>0.605451611824088</v>
       </c>
       <c r="G80" s="1" t="n">
-        <v>10.4514113986012</v>
+        <v>2.68805809220553</v>
       </c>
       <c r="H80" s="1"/>
       <c r="I80" s="1"/>
@@ -2138,10 +2138,10 @@
         <v>0.665312848813308</v>
       </c>
       <c r="F81" s="1" t="n">
-        <v>0.628172424920765</v>
+        <v>0.596465081337533</v>
       </c>
       <c r="G81" s="1" t="n">
-        <v>10.4514113986012</v>
+        <v>2.68805809220553</v>
       </c>
       <c r="H81" s="1"/>
       <c r="I81" s="1"/>
@@ -2160,10 +2160,10 @@
         <v>0.699728691896397</v>
       </c>
       <c r="F82" s="1" t="n">
-        <v>0.508313397553837</v>
+        <v>0.62029446521814</v>
       </c>
       <c r="G82" s="1" t="n">
-        <v>10.4514113986012</v>
+        <v>2.68805809220553</v>
       </c>
       <c r="H82" s="1"/>
       <c r="I82" s="1"/>
@@ -2182,10 +2182,10 @@
         <v>0.71705749329221</v>
       </c>
       <c r="F83" s="1" t="n">
-        <v>0.439434576425384</v>
+        <v>0.647406061291204</v>
       </c>
       <c r="G83" s="1" t="n">
-        <v>10.4514113986012</v>
+        <v>2.68805809220553</v>
       </c>
       <c r="H83" s="1"/>
       <c r="I83" s="1"/>
@@ -2204,10 +2204,10 @@
         <v>0.75169684613473</v>
       </c>
       <c r="F84" s="1" t="n">
-        <v>0.289238212527479</v>
+        <v>0.672542458811773</v>
       </c>
       <c r="G84" s="1" t="n">
-        <v>10.4514113986012</v>
+        <v>2.68805809220553</v>
       </c>
       <c r="H84" s="1"/>
       <c r="I84" s="1"/>
@@ -2226,10 +2226,10 @@
         <v>0.816550796348083</v>
       </c>
       <c r="F85" s="1" t="n">
-        <v>0.0661318886153866</v>
+        <v>0.717274393491469</v>
       </c>
       <c r="G85" s="1" t="n">
-        <v>10.4514113986012</v>
+        <v>2.68805809220553</v>
       </c>
       <c r="H85" s="1"/>
       <c r="I85" s="1"/>
@@ -2248,10 +2248,10 @@
         <v>0.83703950041711</v>
       </c>
       <c r="F86" s="1" t="n">
-        <v>0.130048862021205</v>
+        <v>0.738067311335151</v>
       </c>
       <c r="G86" s="1" t="n">
-        <v>10.4514113986012</v>
+        <v>2.68805809220553</v>
       </c>
       <c r="H86" s="1"/>
       <c r="I86" s="1"/>
@@ -2270,10 +2270,10 @@
         <v>0.868382731456832</v>
       </c>
       <c r="F87" s="1" t="n">
-        <v>0.296482680504361</v>
+        <v>0.802888580753353</v>
       </c>
       <c r="G87" s="1" t="n">
-        <v>10.4514113986012</v>
+        <v>2.68805809220553</v>
       </c>
       <c r="H87" s="1"/>
       <c r="I87" s="1"/>
@@ -2292,10 +2292,10 @@
         <v>0.93059740881718</v>
       </c>
       <c r="F88" s="1" t="n">
-        <v>0.615150190249191</v>
+        <v>0.841531555750145</v>
       </c>
       <c r="G88" s="1" t="n">
-        <v>10.4514113986012</v>
+        <v>2.68805809220553</v>
       </c>
       <c r="H88" s="1"/>
       <c r="I88" s="1"/>
@@ -2314,10 +2314,10 @@
         <v>0.973848688893507</v>
       </c>
       <c r="F89" s="1" t="n">
-        <v>0.862982686933062</v>
+        <v>0.894380835417212</v>
       </c>
       <c r="G89" s="1" t="n">
-        <v>10.4514113986012</v>
+        <v>2.68805809220553</v>
       </c>
       <c r="H89" s="1"/>
       <c r="I89" s="1"/>
@@ -2336,10 +2336,10 @@
         <v>1.06029314679948</v>
       </c>
       <c r="F90" s="1" t="n">
-        <v>1.33892626820624</v>
+        <v>1.10429135339107</v>
       </c>
       <c r="G90" s="1" t="n">
-        <v>10.4514113986012</v>
+        <v>2.68805809220553</v>
       </c>
       <c r="H90" s="1"/>
       <c r="I90" s="1"/>
@@ -2358,10 +2358,10 @@
         <v>1.13832928703449</v>
       </c>
       <c r="F91" s="1" t="n">
-        <v>1.78414350769471</v>
+        <v>1.40719034797924</v>
       </c>
       <c r="G91" s="1" t="n">
-        <v>10.4514113986012</v>
+        <v>2.68805809220553</v>
       </c>
       <c r="H91" s="1"/>
       <c r="I91" s="1"/>
@@ -2380,10 +2380,10 @@
         <v>1.24804147373319</v>
       </c>
       <c r="F92" s="1" t="n">
-        <v>2.4293932833134</v>
+        <v>1.63168935027186</v>
       </c>
       <c r="G92" s="1" t="n">
-        <v>10.4514113986012</v>
+        <v>2.68805809220553</v>
       </c>
       <c r="H92" s="1"/>
       <c r="I92" s="1"/>
@@ -2402,10 +2402,10 @@
         <v>1.44711250604127</v>
       </c>
       <c r="F93" s="1" t="n">
-        <v>3.64314762203906</v>
+        <v>2.38939360028552</v>
       </c>
       <c r="G93" s="1" t="n">
-        <v>10.4514113986012</v>
+        <v>2.68805809220553</v>
       </c>
       <c r="H93" s="1"/>
       <c r="I93" s="1"/>
@@ -2424,10 +2424,10 @@
         <v>1.67917928780924</v>
       </c>
       <c r="F94" s="1" t="n">
-        <v>5.10805579005869</v>
+        <v>3.49495828211445</v>
       </c>
       <c r="G94" s="1" t="n">
-        <v>10.4514113986012</v>
+        <v>2.68805809220553</v>
       </c>
       <c r="H94" s="1"/>
       <c r="I94" s="1"/>
@@ -2446,10 +2446,10 @@
         <v>2.06130372185612</v>
       </c>
       <c r="F95" s="1" t="n">
-        <v>7.59915773003552</v>
+        <v>5.10476910102161</v>
       </c>
       <c r="G95" s="1" t="n">
-        <v>10.4514113986012</v>
+        <v>2.68805809220553</v>
       </c>
       <c r="H95" s="1"/>
       <c r="I95" s="1"/>
